--- a/convergencia_SEM_estab_25.xlsx
+++ b/convergencia_SEM_estab_25.xlsx
@@ -12,6 +12,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rc101_g30_G50_SM20" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rc101_g30_G100_SM20" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c101N_g10_G50_SM15" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c101N_g10_G50_SM200" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c105_g10_G50_SM200" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c105_g10_G100_SM200" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c105_g10_G200_SM200" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c105_g10_G75_SM200" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c105_g10_G300_SM200" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c105_g10_G500_SM200" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c107_g10_G50_SM200" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c107_g10_G100_SM200" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c107_g10_G200_SM200" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c107_g10_G75_SM200" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c107_g10_G300_SM200" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c107_g10_G500_SM200" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,6 +664,1615 @@
       </c>
       <c r="K5" t="n">
         <v>462</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>c101N_g10_G50_SM200</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>c101N</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G6" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>180</v>
+      </c>
+      <c r="K6" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>c105_g10_G50_SM200</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>c105</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>c105_g10_G100_SM200</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>c105</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>c105_g10_G75_SM200</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>c105</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>75</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>c105_g10_G200_SM200</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>c105</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G10" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>c105_g10_G300_SM200</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>c105</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G11" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>c105_g10_G500_SM200</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>c105</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G12" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>c107_g10_G50_SM200</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>c107</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>c107_g10_G100_SM200</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>c107</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G14" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>c107_g10_G75_SM200</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>c107</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>200</v>
+      </c>
+      <c r="G15" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>c107_g10_G200_SM200</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>c107</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>200</v>
+      </c>
+      <c r="F16" t="n">
+        <v>200</v>
+      </c>
+      <c r="G16" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>c107_g10_G300_SM200</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>c107</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>300</v>
+      </c>
+      <c r="F17" t="n">
+        <v>200</v>
+      </c>
+      <c r="G17" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>c107_g10_G500_SM200</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>c107</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEM_estab</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>500</v>
+      </c>
+      <c r="F18" t="n">
+        <v>200</v>
+      </c>
+      <c r="G18" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2361936569213867</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2367470264434814</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2419159412384033</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2424898147583008</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.283677339553833</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2847120761871338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3285644054412842</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3292019367218018</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4087767601013184</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4095549583435059</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3277895450592041</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3284139633178711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3611059188842773</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3618946075439453</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3510482311248779</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3515968322753906</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3066635131835938</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c107.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3071982860565186</v>
       </c>
     </row>
   </sheetData>
@@ -20574,10 +22196,6 @@
       <c r="D2" t="n">
         <v>120116.3</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>80</v>
       </c>
@@ -20600,10 +22218,6 @@
       <c r="D3" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>82</v>
       </c>
@@ -20626,10 +22240,6 @@
       <c r="D4" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>84</v>
       </c>
@@ -20652,10 +22262,6 @@
       <c r="D5" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>86</v>
       </c>
@@ -20678,10 +22284,6 @@
       <c r="D6" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>89</v>
       </c>
@@ -20704,10 +22306,6 @@
       <c r="D7" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>92</v>
       </c>
@@ -20730,10 +22328,6 @@
       <c r="D8" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>94</v>
       </c>
@@ -20756,10 +22350,6 @@
       <c r="D9" t="n">
         <v>40266.5</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>96</v>
       </c>
@@ -20782,10 +22372,6 @@
       <c r="D10" t="n">
         <v>36316.17999999999</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>98</v>
       </c>
@@ -20808,10 +22394,6 @@
       <c r="D11" t="n">
         <v>31976.43333333334</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>101</v>
       </c>
@@ -20834,10 +22416,6 @@
       <c r="D12" t="n">
         <v>26328.3</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>103</v>
       </c>
@@ -20860,10 +22438,6 @@
       <c r="D13" t="n">
         <v>26328.3</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>106</v>
       </c>
@@ -20886,10 +22460,6 @@
       <c r="D14" t="n">
         <v>25669.05333333333</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>107</v>
       </c>
@@ -20912,10 +22482,6 @@
       <c r="D15" t="n">
         <v>22881.54576271187</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>108</v>
       </c>
@@ -20938,10 +22504,6 @@
       <c r="D16" t="n">
         <v>22738.23489096573</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>110</v>
       </c>
@@ -20964,10 +22526,6 @@
       <c r="D17" t="n">
         <v>21762.51689189189</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>113</v>
       </c>
@@ -20990,10 +22548,6 @@
       <c r="D18" t="n">
         <v>20714.62962962963</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>115</v>
       </c>
@@ -21016,10 +22570,6 @@
       <c r="D19" t="n">
         <v>18693.65833333333</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>117</v>
       </c>
@@ -21042,10 +22592,6 @@
       <c r="D20" t="n">
         <v>16528.74409566517</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>118</v>
       </c>
@@ -21068,10 +22614,6 @@
       <c r="D21" t="n">
         <v>16275.34830188679</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>121</v>
       </c>
@@ -21094,10 +22636,6 @@
       <c r="D22" t="n">
         <v>15360.07077922078</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>124</v>
       </c>
@@ -21120,10 +22658,6 @@
       <c r="D23" t="n">
         <v>15173.21582733813</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>126</v>
       </c>
@@ -21146,10 +22680,6 @@
       <c r="D24" t="n">
         <v>15038.5812769629</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>129</v>
       </c>
@@ -21172,10 +22702,6 @@
       <c r="D25" t="n">
         <v>14746.33439153438</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>132</v>
       </c>
@@ -21198,10 +22724,6 @@
       <c r="D26" t="n">
         <v>14125.79108910892</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>133</v>
       </c>
@@ -21224,10 +22746,6 @@
       <c r="D27" t="n">
         <v>13244.5440860215</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>136</v>
       </c>
@@ -21250,10 +22768,6 @@
       <c r="D28" t="n">
         <v>13065.588950583</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>139</v>
       </c>
@@ -21276,10 +22790,6 @@
       <c r="D29" t="n">
         <v>12077.23168103448</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>142</v>
       </c>
@@ -21302,10 +22812,6 @@
       <c r="D30" t="n">
         <v>11026.72193732194</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>145</v>
       </c>
@@ -21328,10 +22834,6 @@
       <c r="D31" t="n">
         <v>10714.00654648956</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>147</v>
       </c>
@@ -21354,10 +22856,6 @@
       <c r="D32" t="n">
         <v>8668.4</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>150</v>
       </c>
@@ -21380,10 +22878,6 @@
       <c r="D33" t="n">
         <v>8105.266183035722</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>153</v>
       </c>
@@ -21406,10 +22900,6 @@
       <c r="D34" t="n">
         <v>6692.208534322824</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>156</v>
       </c>
@@ -21432,10 +22922,6 @@
       <c r="D35" t="n">
         <v>6319.030361691293</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>159</v>
       </c>
@@ -21458,10 +22944,6 @@
       <c r="D36" t="n">
         <v>5502.096848739493</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>161</v>
       </c>
@@ -21484,10 +22966,6 @@
       <c r="D37" t="n">
         <v>5492.174473684212</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>164</v>
       </c>
@@ -21510,10 +22988,6 @@
       <c r="D38" t="n">
         <v>5485.226515151518</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>165</v>
       </c>
@@ -21536,10 +23010,6 @@
       <c r="D39" t="n">
         <v>4131.719270833337</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>167</v>
       </c>
@@ -21562,10 +23032,6 @@
       <c r="D40" t="n">
         <v>4103.524435028248</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>168</v>
       </c>
@@ -21588,10 +23054,6 @@
       <c r="D41" t="n">
         <v>3942.72026066351</v>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>169</v>
       </c>
@@ -21614,10 +23076,6 @@
       <c r="D42" t="n">
         <v>3940.161597281229</v>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>172</v>
       </c>
@@ -21640,10 +23098,6 @@
       <c r="D43" t="n">
         <v>3861.465802269038</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>175</v>
       </c>
@@ -21666,10 +23120,6 @@
       <c r="D44" t="n">
         <v>3810.756756756753</v>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>176</v>
       </c>
@@ -21692,10 +23142,6 @@
       <c r="D45" t="n">
         <v>3762.118260869568</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>177</v>
       </c>
@@ -21718,10 +23164,6 @@
       <c r="D46" t="n">
         <v>3469.930836820085</v>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>180</v>
       </c>
@@ -21744,10 +23186,6 @@
       <c r="D47" t="n">
         <v>3451.870481927732</v>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>183</v>
       </c>
@@ -21770,10 +23208,6 @@
       <c r="D48" t="n">
         <v>2981.855691056903</v>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>186</v>
       </c>
@@ -21796,10 +23230,6 @@
       <c r="D49" t="n">
         <v>2961.8293207801</v>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>189</v>
       </c>
@@ -21822,10 +23252,6 @@
       <c r="D50" t="n">
         <v>2901.253846153846</v>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>191</v>
       </c>
@@ -21848,10 +23274,6 @@
       <c r="D51" t="n">
         <v>2877.895744680849</v>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>192</v>
       </c>
@@ -21874,10 +23296,6 @@
       <c r="D52" t="n">
         <v>2779.505115089514</v>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>194</v>
       </c>
@@ -21900,10 +23318,6 @@
       <c r="D53" t="n">
         <v>2463.600946745564</v>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>197</v>
       </c>
@@ -21926,10 +23340,6 @@
       <c r="D54" t="n">
         <v>2309.396873398256</v>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>198</v>
       </c>
@@ -21952,10 +23362,6 @@
       <c r="D55" t="n">
         <v>2255.318944519623</v>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>201</v>
       </c>
@@ -21978,10 +23384,6 @@
       <c r="D56" t="n">
         <v>2245.338594110463</v>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>202</v>
       </c>
@@ -22004,10 +23406,6 @@
       <c r="D57" t="n">
         <v>2136.30672757475</v>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>204</v>
       </c>
@@ -22030,10 +23428,6 @@
       <c r="D58" t="n">
         <v>1821.034999999998</v>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>205</v>
       </c>
@@ -22056,10 +23450,6 @@
       <c r="D59" t="n">
         <v>1456.820321552723</v>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>208</v>
       </c>
@@ -22082,10 +23472,6 @@
       <c r="D60" t="n">
         <v>1435.180776243808</v>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>211</v>
       </c>
@@ -22108,10 +23494,6 @@
       <c r="D61" t="n">
         <v>1383.879886914372</v>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>212</v>
       </c>
@@ -22134,10 +23516,6 @@
       <c r="D62" t="n">
         <v>1340.793803418802</v>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>213</v>
       </c>
@@ -22160,10 +23538,6 @@
       <c r="D63" t="n">
         <v>1027.335714285714</v>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>216</v>
       </c>
@@ -22186,10 +23560,6 @@
       <c r="D64" t="n">
         <v>1012.154385964914</v>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>217</v>
       </c>
@@ -22212,10 +23582,6 @@
       <c r="D65" t="n">
         <v>994.0435064935069</v>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>218</v>
       </c>
@@ -22238,10 +23604,6 @@
       <c r="D66" t="n">
         <v>862.5068493150671</v>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>219</v>
       </c>
@@ -22264,10 +23626,6 @@
       <c r="D67" t="n">
         <v>862.5068493150661</v>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>220</v>
       </c>
@@ -22290,10 +23648,6 @@
       <c r="D68" t="n">
         <v>862.5068493150665</v>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>223</v>
       </c>
@@ -22316,10 +23670,6 @@
       <c r="D69" t="n">
         <v>782.6180783818022</v>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>226</v>
       </c>
@@ -22342,10 +23692,6 @@
       <c r="D70" t="n">
         <v>771.2360049321836</v>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>228</v>
       </c>
@@ -22368,10 +23714,6 @@
       <c r="D71" t="n">
         <v>735.837894736841</v>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>229</v>
       </c>
@@ -22394,10 +23736,6 @@
       <c r="D72" t="n">
         <v>690.7754716981142</v>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>231</v>
       </c>
@@ -22420,10 +23758,6 @@
       <c r="D73" t="n">
         <v>685.9105590062107</v>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>232</v>
       </c>
@@ -22446,10 +23780,6 @@
       <c r="D74" t="n">
         <v>500.1550239234459</v>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>234</v>
       </c>
@@ -22472,10 +23802,6 @@
       <c r="D75" t="n">
         <v>500.1550239234477</v>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>237</v>
       </c>
@@ -22498,10 +23824,6 @@
       <c r="D76" t="n">
         <v>485.2254945054906</v>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
         <v>240</v>
       </c>
@@ -22524,10 +23846,6 @@
       <c r="D77" t="n">
         <v>458.7398886827462</v>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>243</v>
       </c>
@@ -22550,10 +23868,6 @@
       <c r="D78" t="n">
         <v>418.6966666666675</v>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
         <v>246</v>
       </c>
@@ -22576,10 +23890,6 @@
       <c r="D79" t="n">
         <v>307.9692307692308</v>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>247</v>
       </c>
@@ -22602,10 +23912,6 @@
       <c r="D80" t="n">
         <v>306.4888888888889</v>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
         <v>249</v>
       </c>
@@ -22628,10 +23934,6 @@
       <c r="D81" t="n">
         <v>306.4888888888888</v>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>250</v>
       </c>
@@ -22654,10 +23956,6 @@
       <c r="D82" t="n">
         <v>306.4888888888889</v>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>251</v>
       </c>
@@ -22680,10 +23978,6 @@
       <c r="D83" t="n">
         <v>306.4888888888888</v>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>254</v>
       </c>
@@ -22706,10 +24000,6 @@
       <c r="D84" t="n">
         <v>306.4888888888889</v>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>257</v>
       </c>
@@ -22732,10 +24022,6 @@
       <c r="D85" t="n">
         <v>304.2732142857143</v>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>260</v>
       </c>
@@ -22758,10 +24044,6 @@
       <c r="D86" t="n">
         <v>300.5642857142857</v>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
         <v>263</v>
       </c>
@@ -22784,10 +24066,6 @@
       <c r="D87" t="n">
         <v>300.5642857142856</v>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
         <v>266</v>
       </c>
@@ -22810,10 +24088,6 @@
       <c r="D88" t="n">
         <v>300.5642857142857</v>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>268</v>
       </c>
@@ -22836,10 +24110,6 @@
       <c r="D89" t="n">
         <v>300.5642857142857</v>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>270</v>
       </c>
@@ -22862,10 +24132,6 @@
       <c r="D90" t="n">
         <v>299.890625</v>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
         <v>272</v>
       </c>
@@ -22888,10 +24154,6 @@
       <c r="D91" t="n">
         <v>292.5963414634145</v>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
         <v>275</v>
       </c>
@@ -22914,10 +24176,6 @@
       <c r="D92" t="n">
         <v>291.2133757961783</v>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
         <v>276</v>
       </c>
@@ -22940,10 +24198,6 @@
       <c r="D93" t="n">
         <v>289.3783783783784</v>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
         <v>278</v>
       </c>
@@ -22966,10 +24220,6 @@
       <c r="D94" t="n">
         <v>276.719298245614</v>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
         <v>281</v>
       </c>
@@ -22992,10 +24242,6 @@
       <c r="D95" t="n">
         <v>276.7192982456141</v>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
         <v>283</v>
       </c>
@@ -23018,10 +24264,6 @@
       <c r="D96" t="n">
         <v>276.417880794702</v>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
         <v>285</v>
       </c>
@@ -23044,10 +24286,6 @@
       <c r="D97" t="n">
         <v>272.225</v>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
         <v>287</v>
       </c>
@@ -23070,10 +24308,6 @@
       <c r="D98" t="n">
         <v>258.8910714285714</v>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
         <v>290</v>
       </c>
@@ -23096,10 +24330,6 @@
       <c r="D99" t="n">
         <v>258.8910714285715</v>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
         <v>293</v>
       </c>
@@ -23122,10 +24352,6 @@
       <c r="D100" t="n">
         <v>253.4526315789474</v>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
         <v>295</v>
       </c>
@@ -23148,10 +24374,6 @@
       <c r="D101" t="n">
         <v>253.4526315789473</v>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
         <v>296</v>
       </c>
@@ -23174,10 +24396,6 @@
       <c r="D102" t="n">
         <v>253.4526315789473</v>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
         <v>298</v>
       </c>
@@ -23200,10 +24418,6 @@
       <c r="D103" t="n">
         <v>247.92</v>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
         <v>301</v>
       </c>
@@ -23226,10 +24440,6 @@
       <c r="D104" t="n">
         <v>245.0363636363637</v>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
         <v>303</v>
       </c>
@@ -23252,10 +24462,6 @@
       <c r="D105" t="n">
         <v>245.0363636363637</v>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
         <v>304</v>
       </c>
@@ -23278,10 +24484,6 @@
       <c r="D106" t="n">
         <v>245.0363636363635</v>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
         <v>306</v>
       </c>
@@ -23304,10 +24506,6 @@
       <c r="D107" t="n">
         <v>245.0363636363636</v>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
         <v>309</v>
       </c>
@@ -23330,10 +24528,6 @@
       <c r="D108" t="n">
         <v>244.2212121212121</v>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
         <v>311</v>
       </c>
@@ -23356,10 +24550,6 @@
       <c r="D109" t="n">
         <v>239.0948717948718</v>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
         <v>313</v>
       </c>
@@ -23382,10 +24572,6 @@
       <c r="D110" t="n">
         <v>237.9208333333333</v>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
         <v>315</v>
       </c>
@@ -23408,10 +24594,6 @@
       <c r="D111" t="n">
         <v>237.9208333333333</v>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
         <v>318</v>
       </c>
@@ -23434,10 +24616,6 @@
       <c r="D112" t="n">
         <v>237.9208333333333</v>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
         <v>321</v>
       </c>
@@ -23460,10 +24638,6 @@
       <c r="D113" t="n">
         <v>237.6124999999998</v>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
         <v>322</v>
       </c>
@@ -23486,10 +24660,6 @@
       <c r="D114" t="n">
         <v>237.6125</v>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
         <v>323</v>
       </c>
@@ -23512,10 +24682,6 @@
       <c r="D115" t="n">
         <v>235.3666666666666</v>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
         <v>326</v>
       </c>
@@ -23538,10 +24704,6 @@
       <c r="D116" t="n">
         <v>234.8411764705883</v>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
         <v>329</v>
       </c>
@@ -23564,10 +24726,6 @@
       <c r="D117" t="n">
         <v>234.8411764705882</v>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
         <v>331</v>
       </c>
@@ -23590,10 +24748,6 @@
       <c r="D118" t="n">
         <v>234.8411764705882</v>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
         <v>333</v>
       </c>
@@ -23616,10 +24770,6 @@
       <c r="D119" t="n">
         <v>232.3857142857143</v>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
         <v>335</v>
       </c>
@@ -23642,10 +24792,6 @@
       <c r="D120" t="n">
         <v>232.3857142857143</v>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
         <v>337</v>
       </c>
@@ -23668,10 +24814,6 @@
       <c r="D121" t="n">
         <v>232.3857142857143</v>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
         <v>338</v>
       </c>
@@ -23694,10 +24836,6 @@
       <c r="D122" t="n">
         <v>232.3857142857143</v>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
         <v>341</v>
       </c>
@@ -23720,10 +24858,6 @@
       <c r="D123" t="n">
         <v>232.3857142857143</v>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
         <v>344</v>
       </c>
@@ -23746,10 +24880,6 @@
       <c r="D124" t="n">
         <v>228.9391304347826</v>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
         <v>345</v>
       </c>
@@ -23772,10 +24902,6 @@
       <c r="D125" t="n">
         <v>228.9391304347826</v>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
         <v>347</v>
       </c>
@@ -23798,10 +24924,6 @@
       <c r="D126" t="n">
         <v>228.9391304347826</v>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
         <v>348</v>
       </c>
@@ -23824,10 +24946,6 @@
       <c r="D127" t="n">
         <v>227.5500000000001</v>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
         <v>349</v>
       </c>
@@ -23850,10 +24968,6 @@
       <c r="D128" t="n">
         <v>224.4413793103448</v>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
         <v>351</v>
       </c>
@@ -23876,10 +24990,6 @@
       <c r="D129" t="n">
         <v>219.983606557377</v>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
         <v>353</v>
       </c>
@@ -23902,10 +25012,6 @@
       <c r="D130" t="n">
         <v>219.8387096774193</v>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
         <v>354</v>
       </c>
@@ -23928,10 +25034,6 @@
       <c r="D131" t="n">
         <v>219.8387096774194</v>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
         <v>356</v>
       </c>
@@ -23954,10 +25056,6 @@
       <c r="D132" t="n">
         <v>219.8387096774193</v>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
         <v>359</v>
       </c>
@@ -23980,10 +25078,6 @@
       <c r="D133" t="n">
         <v>219.5371428571429</v>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
         <v>361</v>
       </c>
@@ -24006,10 +25100,6 @@
       <c r="D134" t="n">
         <v>219.5371428571428</v>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
         <v>363</v>
       </c>
@@ -24032,10 +25122,6 @@
       <c r="D135" t="n">
         <v>219.5371428571428</v>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
         <v>365</v>
       </c>
@@ -24058,10 +25144,6 @@
       <c r="D136" t="n">
         <v>219.5371428571428</v>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
         <v>367</v>
       </c>
@@ -24084,10 +25166,6 @@
       <c r="D137" t="n">
         <v>219.5371428571428</v>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
         <v>369</v>
       </c>
@@ -24110,10 +25188,6 @@
       <c r="D138" t="n">
         <v>217.7</v>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
         <v>371</v>
       </c>
@@ -24136,10 +25210,6 @@
       <c r="D139" t="n">
         <v>217.7</v>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
         <v>372</v>
       </c>
@@ -24162,10 +25232,6 @@
       <c r="D140" t="n">
         <v>217.7</v>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
         <v>374</v>
       </c>
@@ -24188,10 +25254,6 @@
       <c r="D141" t="n">
         <v>217.7</v>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
         <v>375</v>
       </c>
@@ -24214,10 +25276,6 @@
       <c r="D142" t="n">
         <v>217.7</v>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
         <v>377</v>
       </c>
@@ -24240,10 +25298,6 @@
       <c r="D143" t="n">
         <v>217.7</v>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
         <v>379</v>
       </c>
@@ -24266,10 +25320,6 @@
       <c r="D144" t="n">
         <v>217.7</v>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
         <v>382</v>
       </c>
@@ -24292,10 +25342,6 @@
       <c r="D145" t="n">
         <v>217.7</v>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
         <v>384</v>
       </c>
@@ -24318,10 +25364,6 @@
       <c r="D146" t="n">
         <v>217.7</v>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
         <v>387</v>
       </c>
@@ -24344,10 +25386,6 @@
       <c r="D147" t="n">
         <v>217.7</v>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
         <v>389</v>
       </c>
@@ -24370,10 +25408,6 @@
       <c r="D148" t="n">
         <v>217.7</v>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
         <v>392</v>
       </c>
@@ -24396,10 +25430,6 @@
       <c r="D149" t="n">
         <v>217.7</v>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
         <v>395</v>
       </c>
@@ -24422,10 +25452,6 @@
       <c r="D150" t="n">
         <v>214.5733333333333</v>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
         <v>397</v>
       </c>
@@ -24448,10 +25474,6 @@
       <c r="D151" t="n">
         <v>214.5733333333333</v>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
         <v>399</v>
       </c>
@@ -24474,10 +25496,6 @@
       <c r="D152" t="n">
         <v>214.5733333333333</v>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
         <v>402</v>
       </c>
@@ -24500,10 +25518,6 @@
       <c r="D153" t="n">
         <v>213.844</v>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
         <v>405</v>
       </c>
@@ -24526,10 +25540,6 @@
       <c r="D154" t="n">
         <v>213.1636363636364</v>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
         <v>407</v>
       </c>
@@ -24552,10 +25562,6 @@
       <c r="D155" t="n">
         <v>213.05625</v>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>408</v>
       </c>
@@ -24578,10 +25584,6 @@
       <c r="D156" t="n">
         <v>213.05625</v>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>411</v>
       </c>
@@ -24604,10 +25606,6 @@
       <c r="D157" t="n">
         <v>212.6272727272727</v>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>414</v>
       </c>
@@ -24630,10 +25628,6 @@
       <c r="D158" t="n">
         <v>212.6272727272728</v>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>417</v>
       </c>
@@ -24656,10 +25650,6 @@
       <c r="D159" t="n">
         <v>212.6272727272727</v>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>420</v>
       </c>
@@ -24682,10 +25672,6 @@
       <c r="D160" t="n">
         <v>212.6272727272727</v>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>423</v>
       </c>
@@ -24708,10 +25694,6 @@
       <c r="D161" t="n">
         <v>212.6272727272727</v>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>426</v>
       </c>
@@ -24734,10 +25716,6 @@
       <c r="D162" t="n">
         <v>206.7230769230769</v>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>428</v>
       </c>
@@ -24760,10 +25738,6 @@
       <c r="D163" t="n">
         <v>206.7230769230769</v>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>430</v>
       </c>
@@ -24786,10 +25760,6 @@
       <c r="D164" t="n">
         <v>206.7230769230769</v>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>432</v>
       </c>
@@ -24812,10 +25782,6 @@
       <c r="D165" t="n">
         <v>206.7230769230769</v>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>433</v>
       </c>
@@ -24838,10 +25804,6 @@
       <c r="D166" t="n">
         <v>206.7230769230769</v>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>436</v>
       </c>
@@ -24864,10 +25826,6 @@
       <c r="D167" t="n">
         <v>204.92</v>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>437</v>
       </c>
@@ -24890,10 +25848,6 @@
       <c r="D168" t="n">
         <v>204.92</v>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>438</v>
       </c>
@@ -24916,10 +25870,6 @@
       <c r="D169" t="n">
         <v>204.4571428571429</v>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>439</v>
       </c>
@@ -24942,10 +25892,6 @@
       <c r="D170" t="n">
         <v>204.4571428571429</v>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>440</v>
       </c>
@@ -24968,10 +25914,6 @@
       <c r="D171" t="n">
         <v>204.4571428571429</v>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>441</v>
       </c>
@@ -24994,10 +25936,6 @@
       <c r="D172" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>443</v>
       </c>
@@ -25020,10 +25958,6 @@
       <c r="D173" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>445</v>
       </c>
@@ -25046,10 +25980,6 @@
       <c r="D174" t="n">
         <v>201.3777777777779</v>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>446</v>
       </c>
@@ -25072,10 +26002,6 @@
       <c r="D175" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>449</v>
       </c>
@@ -25098,10 +26024,6 @@
       <c r="D176" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>450</v>
       </c>
@@ -25124,10 +26046,6 @@
       <c r="D177" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>451</v>
       </c>
@@ -25150,10 +26068,6 @@
       <c r="D178" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>454</v>
       </c>
@@ -25176,10 +26090,6 @@
       <c r="D179" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>457</v>
       </c>
@@ -25202,10 +26112,6 @@
       <c r="D180" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>458</v>
       </c>
@@ -25228,10 +26134,6 @@
       <c r="D181" t="n">
         <v>201.3777777777778</v>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>459</v>
       </c>
@@ -25257,7 +26159,6 @@
       <c r="E182" t="n">
         <v>191.3</v>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
         <v>191.3</v>
       </c>
@@ -25269,6 +26170,4420 @@
       </c>
       <c r="J182" t="n">
         <v>216.2350699901581</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J182"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>120116.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1749851703643799</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>82</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2132120132446289</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2514843940734863</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>86</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2925760746002197</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>89</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3334200382232666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>92</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3799529075622559</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>94</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4216921329498291</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40266.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>96</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4675698280334473</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36316.17999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>98</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.519221305847168</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31976.43333333334</v>
+      </c>
+      <c r="I11" t="n">
+        <v>101</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5529971122741699</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>26328.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>103</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6034657955169678</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26328.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>106</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6454780101776123</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25669.05333333333</v>
+      </c>
+      <c r="I14" t="n">
+        <v>107</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6741108894348145</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22881.54576271187</v>
+      </c>
+      <c r="I15" t="n">
+        <v>108</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.7033584117889404</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22738.23489096573</v>
+      </c>
+      <c r="I16" t="n">
+        <v>110</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7345952987670898</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>21762.51689189189</v>
+      </c>
+      <c r="I17" t="n">
+        <v>113</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.77915358543396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20714.62962962963</v>
+      </c>
+      <c r="I18" t="n">
+        <v>115</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8166124820709229</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18693.65833333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>117</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.855060338973999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16528.74409566517</v>
+      </c>
+      <c r="I20" t="n">
+        <v>118</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8946480751037598</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16275.34830188679</v>
+      </c>
+      <c r="I21" t="n">
+        <v>121</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9240691661834717</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15360.07077922078</v>
+      </c>
+      <c r="I22" t="n">
+        <v>124</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9905829429626465</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15173.21582733813</v>
+      </c>
+      <c r="I23" t="n">
+        <v>126</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.026779174804688</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15038.5812769629</v>
+      </c>
+      <c r="I24" t="n">
+        <v>129</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.074480772018433</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14746.33439153438</v>
+      </c>
+      <c r="I25" t="n">
+        <v>132</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.113373994827271</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14125.79108910892</v>
+      </c>
+      <c r="I26" t="n">
+        <v>133</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.153433799743652</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13244.5440860215</v>
+      </c>
+      <c r="I27" t="n">
+        <v>136</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.192757844924927</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13065.588950583</v>
+      </c>
+      <c r="I28" t="n">
+        <v>139</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.224656581878662</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>12077.23168103448</v>
+      </c>
+      <c r="I29" t="n">
+        <v>142</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.257610082626343</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>11026.72193732194</v>
+      </c>
+      <c r="I30" t="n">
+        <v>145</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.293400764465332</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10714.00654648956</v>
+      </c>
+      <c r="I31" t="n">
+        <v>147</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.33652925491333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8668.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>150</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.398058414459229</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8105.266183035722</v>
+      </c>
+      <c r="I33" t="n">
+        <v>153</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.467246055603027</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6692.208534322824</v>
+      </c>
+      <c r="I34" t="n">
+        <v>156</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.513179540634155</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6319.030361691293</v>
+      </c>
+      <c r="I35" t="n">
+        <v>159</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.563395023345947</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5502.096848739493</v>
+      </c>
+      <c r="I36" t="n">
+        <v>161</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.62054181098938</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5492.174473684212</v>
+      </c>
+      <c r="I37" t="n">
+        <v>164</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.677409172058105</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5485.226515151518</v>
+      </c>
+      <c r="I38" t="n">
+        <v>165</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.733770370483398</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4131.719270833337</v>
+      </c>
+      <c r="I39" t="n">
+        <v>167</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.789839744567871</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4103.524435028248</v>
+      </c>
+      <c r="I40" t="n">
+        <v>168</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.854777336120605</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3942.72026066351</v>
+      </c>
+      <c r="I41" t="n">
+        <v>169</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.912422657012939</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3940.161597281229</v>
+      </c>
+      <c r="I42" t="n">
+        <v>172</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.995293855667114</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3861.465802269038</v>
+      </c>
+      <c r="I43" t="n">
+        <v>175</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.068971395492554</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3810.756756756753</v>
+      </c>
+      <c r="I44" t="n">
+        <v>176</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.293830633163452</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3762.118260869568</v>
+      </c>
+      <c r="I45" t="n">
+        <v>177</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.354859352111816</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3469.930836820085</v>
+      </c>
+      <c r="I46" t="n">
+        <v>180</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.448166370391846</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3451.870481927732</v>
+      </c>
+      <c r="I47" t="n">
+        <v>183</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.555425643920898</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2981.855691056903</v>
+      </c>
+      <c r="I48" t="n">
+        <v>186</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.618942022323608</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2961.8293207801</v>
+      </c>
+      <c r="I49" t="n">
+        <v>189</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.687902212142944</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2901.253846153846</v>
+      </c>
+      <c r="I50" t="n">
+        <v>191</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2.799102067947388</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2877.895744680849</v>
+      </c>
+      <c r="I51" t="n">
+        <v>192</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.911306142807007</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2779.505115089514</v>
+      </c>
+      <c r="I52" t="n">
+        <v>194</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3.015631437301636</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2463.600946745564</v>
+      </c>
+      <c r="I53" t="n">
+        <v>197</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.086422443389893</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2309.396873398256</v>
+      </c>
+      <c r="I54" t="n">
+        <v>198</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.145719766616821</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2255.318944519623</v>
+      </c>
+      <c r="I55" t="n">
+        <v>201</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.204162120819092</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2245.338594110463</v>
+      </c>
+      <c r="I56" t="n">
+        <v>202</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.249834537506104</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2136.30672757475</v>
+      </c>
+      <c r="I57" t="n">
+        <v>204</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.317960739135742</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1821.034999999998</v>
+      </c>
+      <c r="I58" t="n">
+        <v>205</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.382947206497192</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1456.820321552723</v>
+      </c>
+      <c r="I59" t="n">
+        <v>208</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.441367149353027</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1435.180776243808</v>
+      </c>
+      <c r="I60" t="n">
+        <v>211</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.4952232837677</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1383.879886914372</v>
+      </c>
+      <c r="I61" t="n">
+        <v>212</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.570790529251099</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1340.793803418802</v>
+      </c>
+      <c r="I62" t="n">
+        <v>213</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.654669284820557</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1027.335714285714</v>
+      </c>
+      <c r="I63" t="n">
+        <v>216</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.717521905899048</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1012.154385964914</v>
+      </c>
+      <c r="I64" t="n">
+        <v>217</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.791886806488037</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>994.0435064935069</v>
+      </c>
+      <c r="I65" t="n">
+        <v>218</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.846800327301025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>862.5068493150671</v>
+      </c>
+      <c r="I66" t="n">
+        <v>219</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.963234424591064</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>862.5068493150661</v>
+      </c>
+      <c r="I67" t="n">
+        <v>220</v>
+      </c>
+      <c r="J67" t="n">
+        <v>4.049074411392212</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>862.5068493150665</v>
+      </c>
+      <c r="I68" t="n">
+        <v>223</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4.119058847427368</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>782.6180783818022</v>
+      </c>
+      <c r="I69" t="n">
+        <v>226</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4.158137798309326</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>771.2360049321836</v>
+      </c>
+      <c r="I70" t="n">
+        <v>228</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4.202878475189209</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>735.837894736841</v>
+      </c>
+      <c r="I71" t="n">
+        <v>229</v>
+      </c>
+      <c r="J71" t="n">
+        <v>4.28082537651062</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>690.7754716981142</v>
+      </c>
+      <c r="I72" t="n">
+        <v>231</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4.365695714950562</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>685.9105590062107</v>
+      </c>
+      <c r="I73" t="n">
+        <v>232</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4.42145299911499</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>500.1550239234459</v>
+      </c>
+      <c r="I74" t="n">
+        <v>234</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4.544712543487549</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>500.1550239234477</v>
+      </c>
+      <c r="I75" t="n">
+        <v>237</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4.695620059967041</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>485.2254945054906</v>
+      </c>
+      <c r="I76" t="n">
+        <v>240</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.768301963806152</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>458.7398886827462</v>
+      </c>
+      <c r="I77" t="n">
+        <v>243</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4.982397794723511</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>418.6966666666675</v>
+      </c>
+      <c r="I78" t="n">
+        <v>246</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5.168987035751343</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>307.9692307692308</v>
+      </c>
+      <c r="I79" t="n">
+        <v>247</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5.296780347824097</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>78</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>306.4888888888889</v>
+      </c>
+      <c r="I80" t="n">
+        <v>249</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5.400612354278564</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>306.4888888888888</v>
+      </c>
+      <c r="I81" t="n">
+        <v>250</v>
+      </c>
+      <c r="J81" t="n">
+        <v>5.485014677047729</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>306.4888888888889</v>
+      </c>
+      <c r="I82" t="n">
+        <v>251</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5.620283842086792</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>81</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>306.4888888888888</v>
+      </c>
+      <c r="I83" t="n">
+        <v>254</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5.68731689453125</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>82</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>306.4888888888889</v>
+      </c>
+      <c r="I84" t="n">
+        <v>257</v>
+      </c>
+      <c r="J84" t="n">
+        <v>5.756737470626831</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>83</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>304.2732142857143</v>
+      </c>
+      <c r="I85" t="n">
+        <v>260</v>
+      </c>
+      <c r="J85" t="n">
+        <v>5.827539920806885</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>84</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>300.5642857142857</v>
+      </c>
+      <c r="I86" t="n">
+        <v>263</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5.913856744766235</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>85</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>300.5642857142856</v>
+      </c>
+      <c r="I87" t="n">
+        <v>266</v>
+      </c>
+      <c r="J87" t="n">
+        <v>6.045540809631348</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>300.5642857142857</v>
+      </c>
+      <c r="I88" t="n">
+        <v>268</v>
+      </c>
+      <c r="J88" t="n">
+        <v>6.156919956207275</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>300.5642857142857</v>
+      </c>
+      <c r="I89" t="n">
+        <v>270</v>
+      </c>
+      <c r="J89" t="n">
+        <v>6.212204933166504</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>299.890625</v>
+      </c>
+      <c r="I90" t="n">
+        <v>272</v>
+      </c>
+      <c r="J90" t="n">
+        <v>6.300825595855713</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>292.5963414634145</v>
+      </c>
+      <c r="I91" t="n">
+        <v>275</v>
+      </c>
+      <c r="J91" t="n">
+        <v>6.396719694137573</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>291.2133757961783</v>
+      </c>
+      <c r="I92" t="n">
+        <v>276</v>
+      </c>
+      <c r="J92" t="n">
+        <v>6.498699188232422</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>289.3783783783784</v>
+      </c>
+      <c r="I93" t="n">
+        <v>278</v>
+      </c>
+      <c r="J93" t="n">
+        <v>6.592962026596069</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>276.719298245614</v>
+      </c>
+      <c r="I94" t="n">
+        <v>281</v>
+      </c>
+      <c r="J94" t="n">
+        <v>6.656798601150513</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>93</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>276.7192982456141</v>
+      </c>
+      <c r="I95" t="n">
+        <v>283</v>
+      </c>
+      <c r="J95" t="n">
+        <v>6.745391607284546</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>94</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>276.417880794702</v>
+      </c>
+      <c r="I96" t="n">
+        <v>285</v>
+      </c>
+      <c r="J96" t="n">
+        <v>6.810253381729126</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>272.225</v>
+      </c>
+      <c r="I97" t="n">
+        <v>287</v>
+      </c>
+      <c r="J97" t="n">
+        <v>6.888167142868042</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>96</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>258.8910714285714</v>
+      </c>
+      <c r="I98" t="n">
+        <v>290</v>
+      </c>
+      <c r="J98" t="n">
+        <v>6.967093467712402</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>258.8910714285715</v>
+      </c>
+      <c r="I99" t="n">
+        <v>293</v>
+      </c>
+      <c r="J99" t="n">
+        <v>7.037800312042236</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>98</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>253.4526315789474</v>
+      </c>
+      <c r="I100" t="n">
+        <v>295</v>
+      </c>
+      <c r="J100" t="n">
+        <v>7.110985994338989</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>99</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>253.4526315789473</v>
+      </c>
+      <c r="I101" t="n">
+        <v>296</v>
+      </c>
+      <c r="J101" t="n">
+        <v>7.190389156341553</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>253.4526315789473</v>
+      </c>
+      <c r="I102" t="n">
+        <v>298</v>
+      </c>
+      <c r="J102" t="n">
+        <v>7.316305637359619</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>101</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="I103" t="n">
+        <v>301</v>
+      </c>
+      <c r="J103" t="n">
+        <v>7.409506559371948</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>102</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>245.0363636363637</v>
+      </c>
+      <c r="I104" t="n">
+        <v>303</v>
+      </c>
+      <c r="J104" t="n">
+        <v>7.508411884307861</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>103</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>245.0363636363637</v>
+      </c>
+      <c r="I105" t="n">
+        <v>304</v>
+      </c>
+      <c r="J105" t="n">
+        <v>7.592130899429321</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>104</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>245.0363636363635</v>
+      </c>
+      <c r="I106" t="n">
+        <v>306</v>
+      </c>
+      <c r="J106" t="n">
+        <v>7.690566301345825</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>105</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>245.0363636363636</v>
+      </c>
+      <c r="I107" t="n">
+        <v>309</v>
+      </c>
+      <c r="J107" t="n">
+        <v>7.910293579101562</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>106</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>244.2212121212121</v>
+      </c>
+      <c r="I108" t="n">
+        <v>311</v>
+      </c>
+      <c r="J108" t="n">
+        <v>8.050310611724854</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>107</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>239.0948717948718</v>
+      </c>
+      <c r="I109" t="n">
+        <v>313</v>
+      </c>
+      <c r="J109" t="n">
+        <v>8.178492546081543</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>237.9208333333333</v>
+      </c>
+      <c r="I110" t="n">
+        <v>315</v>
+      </c>
+      <c r="J110" t="n">
+        <v>8.279601573944092</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>109</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>237.9208333333333</v>
+      </c>
+      <c r="I111" t="n">
+        <v>318</v>
+      </c>
+      <c r="J111" t="n">
+        <v>8.374251365661621</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>110</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>237.9208333333333</v>
+      </c>
+      <c r="I112" t="n">
+        <v>321</v>
+      </c>
+      <c r="J112" t="n">
+        <v>8.529197931289673</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>111</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>237.6124999999998</v>
+      </c>
+      <c r="I113" t="n">
+        <v>322</v>
+      </c>
+      <c r="J113" t="n">
+        <v>8.675044298171997</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>112</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>237.6125</v>
+      </c>
+      <c r="I114" t="n">
+        <v>323</v>
+      </c>
+      <c r="J114" t="n">
+        <v>8.781197547912598</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>113</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>235.3666666666666</v>
+      </c>
+      <c r="I115" t="n">
+        <v>326</v>
+      </c>
+      <c r="J115" t="n">
+        <v>8.897439479827881</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>114</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>234.8411764705883</v>
+      </c>
+      <c r="I116" t="n">
+        <v>329</v>
+      </c>
+      <c r="J116" t="n">
+        <v>9.06015682220459</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>115</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>234.8411764705882</v>
+      </c>
+      <c r="I117" t="n">
+        <v>331</v>
+      </c>
+      <c r="J117" t="n">
+        <v>9.261709690093994</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>116</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>234.8411764705882</v>
+      </c>
+      <c r="I118" t="n">
+        <v>333</v>
+      </c>
+      <c r="J118" t="n">
+        <v>9.392483949661255</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>117</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>232.3857142857143</v>
+      </c>
+      <c r="I119" t="n">
+        <v>335</v>
+      </c>
+      <c r="J119" t="n">
+        <v>9.527649164199829</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>118</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>232.3857142857143</v>
+      </c>
+      <c r="I120" t="n">
+        <v>337</v>
+      </c>
+      <c r="J120" t="n">
+        <v>9.651779651641846</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>119</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>232.3857142857143</v>
+      </c>
+      <c r="I121" t="n">
+        <v>338</v>
+      </c>
+      <c r="J121" t="n">
+        <v>9.887142658233643</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>120</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>232.3857142857143</v>
+      </c>
+      <c r="I122" t="n">
+        <v>341</v>
+      </c>
+      <c r="J122" t="n">
+        <v>10.05382132530212</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>121</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>232.3857142857143</v>
+      </c>
+      <c r="I123" t="n">
+        <v>344</v>
+      </c>
+      <c r="J123" t="n">
+        <v>10.15362405776978</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>122</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>228.9391304347826</v>
+      </c>
+      <c r="I124" t="n">
+        <v>345</v>
+      </c>
+      <c r="J124" t="n">
+        <v>10.33495926856995</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>123</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>228.9391304347826</v>
+      </c>
+      <c r="I125" t="n">
+        <v>347</v>
+      </c>
+      <c r="J125" t="n">
+        <v>10.70593690872192</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>124</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>228.9391304347826</v>
+      </c>
+      <c r="I126" t="n">
+        <v>348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>11.22777605056763</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>125</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>227.5500000000001</v>
+      </c>
+      <c r="I127" t="n">
+        <v>349</v>
+      </c>
+      <c r="J127" t="n">
+        <v>11.52492308616638</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>126</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>224.4413793103448</v>
+      </c>
+      <c r="I128" t="n">
+        <v>351</v>
+      </c>
+      <c r="J128" t="n">
+        <v>11.73117256164551</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>127</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>219.983606557377</v>
+      </c>
+      <c r="I129" t="n">
+        <v>353</v>
+      </c>
+      <c r="J129" t="n">
+        <v>11.95462203025818</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>128</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>219.8387096774193</v>
+      </c>
+      <c r="I130" t="n">
+        <v>354</v>
+      </c>
+      <c r="J130" t="n">
+        <v>12.12264084815979</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>129</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>219.8387096774194</v>
+      </c>
+      <c r="I131" t="n">
+        <v>356</v>
+      </c>
+      <c r="J131" t="n">
+        <v>12.29118084907532</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>219.8387096774193</v>
+      </c>
+      <c r="I132" t="n">
+        <v>359</v>
+      </c>
+      <c r="J132" t="n">
+        <v>12.63170790672302</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>131</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>219.5371428571429</v>
+      </c>
+      <c r="I133" t="n">
+        <v>361</v>
+      </c>
+      <c r="J133" t="n">
+        <v>12.76580834388733</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>132</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>219.5371428571428</v>
+      </c>
+      <c r="I134" t="n">
+        <v>363</v>
+      </c>
+      <c r="J134" t="n">
+        <v>12.94617080688477</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>133</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>219.5371428571428</v>
+      </c>
+      <c r="I135" t="n">
+        <v>365</v>
+      </c>
+      <c r="J135" t="n">
+        <v>13.25552415847778</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>134</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>219.5371428571428</v>
+      </c>
+      <c r="I136" t="n">
+        <v>367</v>
+      </c>
+      <c r="J136" t="n">
+        <v>13.42043089866638</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>135</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>219.5371428571428</v>
+      </c>
+      <c r="I137" t="n">
+        <v>369</v>
+      </c>
+      <c r="J137" t="n">
+        <v>13.71966600418091</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>136</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I138" t="n">
+        <v>371</v>
+      </c>
+      <c r="J138" t="n">
+        <v>13.90612983703613</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>137</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I139" t="n">
+        <v>372</v>
+      </c>
+      <c r="J139" t="n">
+        <v>14.04467749595642</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>138</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I140" t="n">
+        <v>374</v>
+      </c>
+      <c r="J140" t="n">
+        <v>14.22045230865479</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>139</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I141" t="n">
+        <v>375</v>
+      </c>
+      <c r="J141" t="n">
+        <v>14.74748015403748</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>140</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I142" t="n">
+        <v>377</v>
+      </c>
+      <c r="J142" t="n">
+        <v>27.87432456016541</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>141</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I143" t="n">
+        <v>379</v>
+      </c>
+      <c r="J143" t="n">
+        <v>28.01732516288757</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>142</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I144" t="n">
+        <v>382</v>
+      </c>
+      <c r="J144" t="n">
+        <v>36.42056345939636</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>143</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I145" t="n">
+        <v>384</v>
+      </c>
+      <c r="J145" t="n">
+        <v>43.71311187744141</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>144</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I146" t="n">
+        <v>387</v>
+      </c>
+      <c r="J146" t="n">
+        <v>44.07028007507324</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>145</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I147" t="n">
+        <v>389</v>
+      </c>
+      <c r="J147" t="n">
+        <v>44.46596503257751</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>146</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I148" t="n">
+        <v>392</v>
+      </c>
+      <c r="J148" t="n">
+        <v>44.67146563529968</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>147</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="I149" t="n">
+        <v>395</v>
+      </c>
+      <c r="J149" t="n">
+        <v>44.80962133407593</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>148</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>214.5733333333333</v>
+      </c>
+      <c r="I150" t="n">
+        <v>397</v>
+      </c>
+      <c r="J150" t="n">
+        <v>44.94985413551331</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>149</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>214.5733333333333</v>
+      </c>
+      <c r="I151" t="n">
+        <v>399</v>
+      </c>
+      <c r="J151" t="n">
+        <v>45.09281826019287</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>150</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>214.5733333333333</v>
+      </c>
+      <c r="I152" t="n">
+        <v>402</v>
+      </c>
+      <c r="J152" t="n">
+        <v>45.36588621139526</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>151</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>213.844</v>
+      </c>
+      <c r="I153" t="n">
+        <v>405</v>
+      </c>
+      <c r="J153" t="n">
+        <v>45.52817296981812</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>152</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>213.1636363636364</v>
+      </c>
+      <c r="I154" t="n">
+        <v>407</v>
+      </c>
+      <c r="J154" t="n">
+        <v>45.77136564254761</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>153</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>213.05625</v>
+      </c>
+      <c r="I155" t="n">
+        <v>408</v>
+      </c>
+      <c r="J155" t="n">
+        <v>46.00362706184387</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>154</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>213.05625</v>
+      </c>
+      <c r="I156" t="n">
+        <v>411</v>
+      </c>
+      <c r="J156" t="n">
+        <v>46.18475270271301</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>155</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>212.6272727272727</v>
+      </c>
+      <c r="I157" t="n">
+        <v>414</v>
+      </c>
+      <c r="J157" t="n">
+        <v>46.45799088478088</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>156</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>212.6272727272728</v>
+      </c>
+      <c r="I158" t="n">
+        <v>417</v>
+      </c>
+      <c r="J158" t="n">
+        <v>46.613849401474</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>157</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>212.6272727272727</v>
+      </c>
+      <c r="I159" t="n">
+        <v>420</v>
+      </c>
+      <c r="J159" t="n">
+        <v>46.80101084709167</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>158</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>212.6272727272727</v>
+      </c>
+      <c r="I160" t="n">
+        <v>423</v>
+      </c>
+      <c r="J160" t="n">
+        <v>46.95188140869141</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>159</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>212.6272727272727</v>
+      </c>
+      <c r="I161" t="n">
+        <v>426</v>
+      </c>
+      <c r="J161" t="n">
+        <v>54.97867655754089</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>160</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>206.7230769230769</v>
+      </c>
+      <c r="I162" t="n">
+        <v>428</v>
+      </c>
+      <c r="J162" t="n">
+        <v>55.42907047271729</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>161</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>206.7230769230769</v>
+      </c>
+      <c r="I163" t="n">
+        <v>430</v>
+      </c>
+      <c r="J163" t="n">
+        <v>55.63666915893555</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>162</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>206.7230769230769</v>
+      </c>
+      <c r="I164" t="n">
+        <v>432</v>
+      </c>
+      <c r="J164" t="n">
+        <v>55.79452681541443</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>163</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>206.7230769230769</v>
+      </c>
+      <c r="I165" t="n">
+        <v>433</v>
+      </c>
+      <c r="J165" t="n">
+        <v>56.07992935180664</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>164</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>206.7230769230769</v>
+      </c>
+      <c r="I166" t="n">
+        <v>436</v>
+      </c>
+      <c r="J166" t="n">
+        <v>56.32433652877808</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>165</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>204.92</v>
+      </c>
+      <c r="I167" t="n">
+        <v>437</v>
+      </c>
+      <c r="J167" t="n">
+        <v>64.44781374931335</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>166</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>204.92</v>
+      </c>
+      <c r="I168" t="n">
+        <v>438</v>
+      </c>
+      <c r="J168" t="n">
+        <v>64.84127426147461</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>167</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>204.4571428571429</v>
+      </c>
+      <c r="I169" t="n">
+        <v>439</v>
+      </c>
+      <c r="J169" t="n">
+        <v>65.12008428573608</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>168</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>204.4571428571429</v>
+      </c>
+      <c r="I170" t="n">
+        <v>440</v>
+      </c>
+      <c r="J170" t="n">
+        <v>65.43996047973633</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>169</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>204.4571428571429</v>
+      </c>
+      <c r="I171" t="n">
+        <v>441</v>
+      </c>
+      <c r="J171" t="n">
+        <v>73.08110094070435</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>170</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I172" t="n">
+        <v>443</v>
+      </c>
+      <c r="J172" t="n">
+        <v>73.36491966247559</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>171</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I173" t="n">
+        <v>445</v>
+      </c>
+      <c r="J173" t="n">
+        <v>73.55145978927612</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>172</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>201.3777777777779</v>
+      </c>
+      <c r="I174" t="n">
+        <v>446</v>
+      </c>
+      <c r="J174" t="n">
+        <v>73.73196911811829</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>173</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I175" t="n">
+        <v>449</v>
+      </c>
+      <c r="J175" t="n">
+        <v>73.89515662193298</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>174</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I176" t="n">
+        <v>450</v>
+      </c>
+      <c r="J176" t="n">
+        <v>74.21086096763611</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>175</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I177" t="n">
+        <v>451</v>
+      </c>
+      <c r="J177" t="n">
+        <v>74.52277064323425</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>176</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I178" t="n">
+        <v>454</v>
+      </c>
+      <c r="J178" t="n">
+        <v>81.388108253479</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>177</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I179" t="n">
+        <v>457</v>
+      </c>
+      <c r="J179" t="n">
+        <v>88.31883335113525</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>178</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I180" t="n">
+        <v>458</v>
+      </c>
+      <c r="J180" t="n">
+        <v>88.57945513725281</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>179</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>201.3777777777778</v>
+      </c>
+      <c r="I181" t="n">
+        <v>459</v>
+      </c>
+      <c r="J181" t="n">
+        <v>96.47416281700134</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>instancias/c101N.txt</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>180</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E182" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>462</v>
+      </c>
+      <c r="J182" t="n">
+        <v>96.54849171638489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2688496112823486</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2701025009155273</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2833280563354492</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2839267253875732</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>instancia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>iteracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LB_frac</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_iter</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UB_mip_periodico</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>melhor_UB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gap_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_colunas_pool</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.293562650680542</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instancias/c105.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2943034172058105</v>
       </c>
     </row>
   </sheetData>
